--- a/demo_data/sectors/uretim_sanayi/mizan_cur.xlsx
+++ b/demo_data/sectors/uretim_sanayi/mizan_cur.xlsx
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22930.21</v>
+        <v>22930.22</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2097458.9</v>
+        <v>2097458.91</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>28181.29</v>
+        <v>28181.28</v>
       </c>
     </row>
     <row r="53">
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>45080417.78</v>
+        <v>45080417.81</v>
       </c>
     </row>
     <row r="58">
